--- a/Data/Regression Evidence 2025/testDataIreland.xlsx
+++ b/Data/Regression Evidence 2025/testDataIreland.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F432E808-846C-44B9-9CC0-E8429FF8E986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99EFB12A-BED2-453A-97A7-CA074F05E1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,10 +213,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Tiana</t>
-  </si>
-  <si>
-    <t>Huel-Crist</t>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>Gibson</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,7 +285,7 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
-    <t>1234748TW</t>
+    <t>1234758TW</t>
   </si>
   <si>
     <t>Male</t>
@@ -327,13 +327,13 @@
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Alec</t>
-  </si>
-  <si>
-    <t>Wisozk</t>
-  </si>
-  <si>
-    <t>Auto 21279645</t>
+    <t>Madyson</t>
+  </si>
+  <si>
+    <t>Durgan</t>
+  </si>
+  <si>
+    <t>Auto 34006623</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -342,7 +342,7 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234749TW</t>
+    <t>1234759TW</t>
   </si>
   <si>
     <t>IE Management Group 20</t>
@@ -387,6 +387,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -411,14 +419,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -545,7 +545,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -578,10 +578,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -602,7 +602,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -613,7 +613,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
@@ -630,11 +630,10 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1154,9 +1153,9 @@
         <v>57</v>
       </c>
       <c r="B2" s="12">
-        <v>10700246</v>
-      </c>
-      <c r="C2" s="32" t="s">
+        <v>10700451</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D2" s="13" t="s">
@@ -1185,7 +1184,7 @@
       </c>
       <c r="L2" s="18">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>65</v>
@@ -1222,11 +1221,11 @@
       </c>
       <c r="X2" s="22">
         <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45912</v>
+        <v>45933</v>
       </c>
       <c r="Z2" s="17" t="s">
         <v>71</v>
@@ -1339,9 +1338,9 @@
         <v>97</v>
       </c>
       <c r="B3" s="12">
-        <v>10700247</v>
-      </c>
-      <c r="C3" s="32" t="s">
+        <v>10700452</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -1370,7 +1369,7 @@
       </c>
       <c r="L3" s="18">
         <f t="shared" ca="1" si="0"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>65</v>
@@ -1407,11 +1406,11 @@
       </c>
       <c r="X3" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>45912</v>
+        <v>45933</v>
       </c>
       <c r="Z3" s="17" t="s">
         <v>71</v>
